--- a/output/pdf_financials_xlsx/VFI.X.xlsx
+++ b/output/pdf_financials_xlsx/VFI.X.xlsx
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.092721</v>
+        <v>0.147921</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.05281</v>
+        <v>0.100193</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.027365</v>
+        <v>0.058261</v>
       </c>
     </row>
     <row r="11">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.027365</v>
+        <v>-0.058261</v>
       </c>
     </row>
     <row r="12">
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000263</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001263</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000243</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000263</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001263</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000243</v>
       </c>
     </row>
     <row r="37">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">

--- a/output/pdf_financials_xlsx/VFI.X.xlsx
+++ b/output/pdf_financials_xlsx/VFI.X.xlsx
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.09476800000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.09653200000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.096262</v>
       </c>
     </row>
     <row r="68">
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.324352</v>
+        <v>0.41912</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.357905</v>
+        <v>0.454437</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.39426</v>
+        <v>0.490522</v>
       </c>
     </row>
     <row r="69">
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.038671</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.05021</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.137279</v>
+        <v>0.041017</v>
       </c>
     </row>
     <row r="76">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.001729</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -3794,7 +3794,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.001729</v>
       </c>
